--- a/quiz.xlsx
+++ b/quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UserK\Desktop\Project\0Done\202610 funnyquiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531E1546-F1BA-4133-AD4F-4FA37CCCFA5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2AF074-F59D-4419-AF84-9E8D6BFD2238}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="212">
   <si>
     <t>문제</t>
   </si>
@@ -630,6 +630,74 @@
   </si>
   <si>
     <t>매운탕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기통을 거꾸로 하면?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쏟아진다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거꾸로</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽돌</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽돌 100개 중에 1개가 떨어지면 몇 개가 남나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>99개</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문열기/코끼리넣기/문닫기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코끼리를 냉장고에 넣는 방법은?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기린을 냉장고에 넣는 방법은?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>문열기/코끼리빼기/기린넣기/문닫기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사자가 생일 파티를 열었어요. 한 동물이 안왔네요. 누구일까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악어가 사는 강을 건넜는데, 잡아먹히지 않았어요. 왜일까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런데 죽은채로 발견되었어요. 왜일까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>떨어진 벽돌에 맞아서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악어가 생일 파티에 가서</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -991,22 +1059,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1014,7 +1085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1022,7 +1093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1030,7 +1101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1038,7 +1109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1046,7 +1117,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1054,7 +1125,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1062,7 +1133,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1070,7 +1141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1078,7 +1149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1086,7 +1157,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1094,7 +1165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1102,7 +1173,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1110,7 +1181,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1118,7 +1189,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1736,50 +1807,133 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+      <c r="C97" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>186</v>
+      </c>
+      <c r="C98" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" t="s">
+        <v>201</v>
+      </c>
+      <c r="C100" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>203</v>
+      </c>
+      <c r="B101" t="s">
+        <v>202</v>
+      </c>
+      <c r="C101" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>204</v>
+      </c>
+      <c r="B102" t="s">
+        <v>205</v>
+      </c>
+      <c r="C102" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>209</v>
+      </c>
+      <c r="B105" t="s">
+        <v>210</v>
+      </c>
+      <c r="C105" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/quiz.xlsx
+++ b/quiz.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10860" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="600" yWindow="1410" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="퀴즈" sheetId="1" state="visible" r:id="rId1"/>
@@ -39,17 +39,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE066"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +59,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -433,11 +439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="52" customWidth="1" style="2" min="1" max="1"/>
-    <col width="24" customWidth="1" style="2" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1357,7 +1363,7 @@
         </is>
       </c>
     </row>
-    <row r="77" s="2">
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
           <t>미꾸라지보다 더 큰 미꾸라지는?</t>
@@ -1576,7 +1582,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>고추가루를 총으로 쏘면?</t>
+          <t>고춧가루를 총으로 쏘면?</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1661,7 +1667,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>문열기/코끼리넣기/문닫기</t>
+          <t>문 열고 넣고 닫기</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -1678,7 +1684,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>문열기/코끼리빼기/기린넣기/문닫기</t>
+          <t>코끼리 빼고 기린 넣기</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -1690,7 +1696,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>사자가 생일 파티를 열었어요. 한 동물이 안왔네요. 누구일까요?</t>
+          <t>사자가 생일 파티를 열었어요. 한 동물이 안 왔네요. 누구일까요?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1724,7 +1730,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>그런데 죽은채로 발견되었어요. 왜일까요?</t>
+          <t>그런데 죽은 채로 발견되었어요. 왜일까요?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1738,7 +1744,790 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>아이들이 좋아하는 감은?</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>장난감</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>아무것도 못 담는 자루는?</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>빗자루</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>작아도 크다고 하는 나무는?</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>대나무</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>아무도 못 고치는 집은?</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>고집</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>커도 작다고 하는 나무는?</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>소나무</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>엄마가 싫어하는 금은?</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>세금</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>먹을 수 있는 금은?</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>소금</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>도둑이 좋아하는 금은?</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>살금살금</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>미안할 때 먹는 과일은?</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>사과</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>욕 중에서 깨끗한 욕은?</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>목욕</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>비가 많이 오면 나타나는 개는?</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>번개</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>가위 중 가장 큰 가위는?</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>한가위</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>낮인데도 밤이라고 하는 것은?</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>(먹는)밤</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>오른쪽 나라와 왼쪽 나라의 왕은?</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>우왕좌왕</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>소가 내는 웃음소리?</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>우하하</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>끈 시리즈) 머리 아플 때 쓰는 끈은?</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>지끈지끈</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>끈 시리즈) 추울 때 사람들이 찾는 끈은?</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>뜨끈뜨끈</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>끈 시리즈) 운동하는 사람이 좋아하는 끈은?</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>울끈불끈</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>끈 시리즈) 피부가 좋아지는 끈은?</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>매끈매끈</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>끈 시리즈) 부끄러울 때 찾는 끈은?</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>화끈화끈</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>호주의 돈은?</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>호주머니</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>가장 빠른 차는?</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>첫차</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>천하장사가 타는 차는?</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>으라차차</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>도둑이 좋아하는 아이스크림은?</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>보석바</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>화장실에 사는 두 마리의 용은?</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>신사용, 숙녀용</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>똥이 있는 곳에 사는 새는?</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>똥냄새</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>오이가 무를 치면?</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>오이무침</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>아침이면 생기는 나라는?</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>일어나라</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>돼지가 뀌는 방귀는?</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>돈가스</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>높은 곳에서 아이를 낳으면?</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>하이에나</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>곰돌이 푸가 여러 명 있으면?</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>푸들</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>세상에서 가장 작은 시장은?</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>벼룩시장</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>사람들이 좋아하는 영화는?</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>부귀영화</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>두 마리 코끼리가 싸워서 코가 떨어져 나가면?</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>끼리끼리</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>세상에서 가장 큰 컵은?</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>월드컵</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>아껴 먹어야 하는 약은?</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>절약</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>밥 먹으면 찾아오는 거지는?</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>설거지</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>심장의 무게는?</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>네 근(두 근+두 근)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>투명한 집을 영어로 하면?</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>비닐하우스</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>슈퍼에서 일하는 남자?</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>슈퍼맨</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>오뎅을 다섯 글자로 바꾸면?</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>뎅뎅뎅뎅뎅</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>바늘만 가지고 다니는 사람을 다르게 부르면?</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>실 없는 사람</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>손님이 뜸하면 좋아하는 가게는?</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>한의원</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>못사는 사람들을 환영하는 곳은?</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>철물점</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>문을 두드려도 들어오란 소리를 못 듣는 곳은?</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>화장실</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>똑똑한 사람이 많은 곳은?</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>화장실</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>아무리 높은 사람이라도 모자를 벗어야 하는 곳은?</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>이발소</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>깨뜨려야 쓸 수 있는 것은?</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>계란, 달걀</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>쓰레기만 먹고 사는 것은?</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>쓰레기통</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>같은 물건인데 사람마다 다르게 보는 것은?</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>거울</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>쓰기는 쓰는데 읽을 수 없는 것은?</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>모자</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>오래된 것일수록 젊어 보이는 것은?</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>사진</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>아무리 많이 모아도 결국 버리는 것은?</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>쓰레기</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>누르면 사람이 튀어나오게 하는 물건은?</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>초인종</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>가운데 큰 구멍이 났어도 가라앉지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>튜브</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>매일 먹어도 먹어도 배부르지 않는 것은?</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>공기</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>이상해서 만나는 사람은?</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>치과의사</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>때리고 도망갈수록 인기 있는 사람은?</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>야구선수</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>불을 안 끄면 못 자는 사람은?</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>소방관</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>앉으면 보이고, 서면 안 보이는 것은?</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>발바닥</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>보내기 싫으면 어떻게 해야 할까?</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>가위나 바위를 낸다</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>바다와 땅 사이에 있는 것은?</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>와</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>무엇이든 멈추게 만드는 숫자는?</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5(다섯)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>수영을 했는데 머리가 하나도 젖지 않았다. 왜?</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>대머리라서</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>대통령 선거의 반대말은?</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>대통령 앉은 거</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>

--- a/quiz.xlsx
+++ b/quiz.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2419,106 +2419,94 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>이상해서 만나는 사람은?</t>
+          <t>때리고 도망갈수록 인기 있는 사람은?</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>치과의사</t>
+          <t>야구선수</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>때리고 도망갈수록 인기 있는 사람은?</t>
+          <t>불을 안 끄면 못 자는 사람은?</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>야구선수</t>
+          <t>소방관</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>불을 안 끄면 못 자는 사람은?</t>
+          <t>앉으면 보이고, 서면 안 보이는 것은?</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>소방관</t>
+          <t>발바닥</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>앉으면 보이고, 서면 안 보이는 것은?</t>
+          <t>보내기 싫으면 어떻게 해야 할까?</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>발바닥</t>
+          <t>가위나 바위를 낸다</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>보내기 싫으면 어떻게 해야 할까?</t>
+          <t>바다와 땅 사이에 있는 것은?</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>가위나 바위를 낸다</t>
+          <t>와</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>바다와 땅 사이에 있는 것은?</t>
+          <t>무엇이든 멈추게 만드는 숫자는?</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>와</t>
+          <t>5(다섯)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>무엇이든 멈추게 만드는 숫자는?</t>
+          <t>수영을 했는데 머리가 하나도 젖지 않았다. 왜?</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5(다섯)</t>
+          <t>대머리라서</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>수영을 했는데 머리가 하나도 젖지 않았다. 왜?</t>
+          <t>대통령 선거의 반대말은?</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
-        <is>
-          <t>대머리라서</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>대통령 선거의 반대말은?</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
         <is>
           <t>대통령 앉은 거</t>
         </is>
